--- a/Planning/GROW/Progress_Tees_Valley_GROW_Weekly_Plan_Week03_14Sep.xlsx
+++ b/Planning/GROW/Progress_Tees_Valley_GROW_Weekly_Plan_Week03_14Sep.xlsx
@@ -1124,7 +1124,7 @@
     <row r="8" ht="33.75" customHeight="1" s="47">
       <c r="A8" s="55" t="inlineStr">
         <is>
-          <t>SMSC/BV this week: Grow RE begins the festivals-of-light block (Diwali) — pre-teaching ahead of the November festival; photos start the Festivals-of-Light display (EFL: cultural).  PREP: International Day of Peace is Monday of next week.</t>
+          <t>SMSC/BV this week: Grow RE begins the festivals-of-light block (Diwali) — pre-teaching ahead of the November festival; photos start the Festivals-of-Light display (evidence platform: cultural).  PREP: International Day of Peace is Monday of next week.</t>
         </is>
       </c>
       <c r="B8" s="56" t="n"/>
@@ -1332,7 +1332,7 @@
 Targeted questioning to develop reasoning and confidence.
 Ongoing assessment through observation, discussion and marking.
 Positive feedback and opportunities for peer support and collaborative learning.
-LOOP [Feedback Policy]: Voice = mini-whiteboard show-me / re-do, verbal reply [VF, I] → Audience: name the corrected step back and tick the success criteria; [R] on an accurate re-do → EVIDENCE: photo of the practical proof + book note, same day [E: numeracy/vocational — daily EFL].</t>
+LOOP [Feedback Policy]: Voice = mini-whiteboard show-me / re-do, verbal reply [VF, I] → Audience: name the corrected step back and tick the success criteria; [R] on an accurate re-do → EVIDENCE: photo of the practical proof + book note, same day [E: numeracy/vocational — daily evidence platform].</t>
         </is>
       </c>
       <c r="J11" s="64" t="inlineStr">
@@ -1437,7 +1437,7 @@
       <c r="I13" s="64" t="inlineStr">
         <is>
           <t>TA supports each party's pitch prep; teacher acts as returning officer and honours the winning policy (democracy has to be real to land); live feedback at the count.
-LOOP [Feedback Policy]: Voice = campaign video / freeze-frame / card + verbal reply [VF] → Audience: name the strength back + one [NS]; listen to clips fully before tagging, then [R] → EVIDENCE: video/card photo to EFL, same day [E: PfA/citizenship/social enterprise — daily EFL].</t>
+LOOP [Feedback Policy]: Voice = campaign video / freeze-frame / card + verbal reply [VF] → Audience: name the strength back + one [NS]; listen to clips fully before tagging, then [R] → EVIDENCE: video/card photo to evidence platform, same day [E: PfA/citizenship/social enterprise — daily evidence platform].</t>
         </is>
       </c>
       <c r="J13" s="64" t="inlineStr">
